--- a/data/meta_analysis/old/Cat meta-analysis - SMDs.xlsx
+++ b/data/meta_analysis/old/Cat meta-analysis - SMDs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CBF74C-1205-E244-B41E-A1B032F6532E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952474F7-8F72-AF4E-9F74-2E7599FDB9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="16740" xr2:uid="{6CF683D5-C8B8-0C42-9A59-7A45EEDDF505}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>Effect_size_ID</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>Short-term abundance</t>
+  </si>
+  <si>
+    <t>unit_of_replication</t>
   </si>
 </sst>
 </file>
@@ -998,6 +1001,9 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1083,6 +1089,9 @@
       <c r="AC2" s="6" t="s">
         <v>40</v>
       </c>
+      <c r="AD2" s="13" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
@@ -1166,6 +1175,9 @@
       <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="AD3" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="4" spans="1:40" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -1251,6 +1263,9 @@
       <c r="AC4" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="AD4" s="25" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
@@ -1334,6 +1349,9 @@
       <c r="AC5" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="AD5" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="1:40" s="31" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
@@ -1419,7 +1437,9 @@
       <c r="AC6" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="AD6" s="28"/>
+      <c r="AD6" s="28" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="7" spans="1:40" s="35" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="38" t="s">
@@ -1500,6 +1520,9 @@
       </c>
       <c r="AC7" s="35" t="s">
         <v>70</v>
+      </c>
+      <c r="AD7" s="35" t="s">
+        <v>59</v>
       </c>
       <c r="AM7" s="34"/>
       <c r="AN7" s="34"/>
